--- a/neuroimaging conversion structural/Example data NIfTI/reference_data/pdf_pet/sub-0008_ses-01_pet_pdf.xlsx
+++ b/neuroimaging conversion structural/Example data NIfTI/reference_data/pdf_pet/sub-0008_ses-01_pet_pdf.xlsx
@@ -1,6 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <fileVersion appName="libxl" rupBuild="4.6.0"/>
   <workbookPr/>
   <bookViews>
     <workbookView activeTab="0"/>
@@ -390,7 +391,7 @@
         <v>0</v>
       </c>
       <c r="BS1" s="0">
-        <v>0.052506159376388382</v>
+        <v>0.052506159376388383</v>
       </c>
       <c r="BT1" s="0">
         <v>0.02967862291189689</v>
@@ -1278,10 +1279,10 @@
         <v>0.19397317159795646</v>
       </c>
       <c r="E4" s="0">
-        <v>0.090334236675700091</v>
+        <v>0.090334236675700092</v>
       </c>
       <c r="F4" s="0">
-        <v>0.077472669363863308</v>
+        <v>0.077472669363863309</v>
       </c>
       <c r="G4" s="0">
         <v>0.10683760683760683</v>
@@ -1329,13 +1330,13 @@
         <v>0.037181632273656819</v>
       </c>
       <c r="V4" s="0">
-        <v>0.030637254901960786</v>
+        <v>0.030637254901960787</v>
       </c>
       <c r="W4" s="0">
         <v>0</v>
       </c>
       <c r="X4" s="0">
-        <v>0.037900322152738294</v>
+        <v>0.037900322152738295</v>
       </c>
       <c r="Y4" s="0">
         <v>0.026205450733752623</v>
@@ -1536,7 +1537,7 @@
         <v>0</v>
       </c>
       <c r="CM4" s="0">
-        <v>0.018632383081796162</v>
+        <v>0.018632383081796163</v>
       </c>
       <c r="CN4" s="0">
         <v>0.023929169657812877</v>
@@ -1545,7 +1546,7 @@
         <v>0.044080049369655296</v>
       </c>
       <c r="CP4" s="0">
-        <v>0.0039972818483431267</v>
+        <v>0.0039972818483431268</v>
       </c>
       <c r="CQ4" s="0">
         <v>0</v>
@@ -1685,7 +1686,7 @@
         <v>0.092876381536175348</v>
       </c>
       <c r="T5" s="0">
-        <v>0.17755924332445538</v>
+        <v>0.17755924332445539</v>
       </c>
       <c r="U5" s="0">
         <v>0.055772448410485224</v>
@@ -1898,7 +1899,7 @@
         <v>0.012631047113805735</v>
       </c>
       <c r="CM5" s="0">
-        <v>0.018632383081796162</v>
+        <v>0.018632383081796163</v>
       </c>
       <c r="CN5" s="0">
         <v>0.023929169657812877</v>
@@ -2017,7 +2018,7 @@
         <v>0.16611295681063123</v>
       </c>
       <c r="J6" s="0">
-        <v>0.33889634887141123</v>
+        <v>0.33889634887141124</v>
       </c>
       <c r="K6" s="0">
         <v>0.20904599011782593</v>
@@ -2053,7 +2054,7 @@
         <v>0.055772448410485224</v>
       </c>
       <c r="V6" s="0">
-        <v>0.030637254901960786</v>
+        <v>0.030637254901960787</v>
       </c>
       <c r="W6" s="0">
         <v>0</v>
@@ -2140,7 +2141,7 @@
         <v>0.010128633647320976</v>
       </c>
       <c r="AY6" s="0">
-        <v>0.020222446916076844</v>
+        <v>0.020222446916076845</v>
       </c>
       <c r="AZ6" s="0">
         <v>0.012350253180190195</v>
@@ -2167,7 +2168,7 @@
         <v>0.0061614294516327784</v>
       </c>
       <c r="BH6" s="0">
-        <v>0.022311468094600623</v>
+        <v>0.022311468094600624</v>
       </c>
       <c r="BI6" s="0">
         <v>0.01793078716155639</v>
@@ -2200,10 +2201,10 @@
         <v>0</v>
       </c>
       <c r="BS6" s="0">
-        <v>0.080778706732905214</v>
+        <v>0.080778706732905215</v>
       </c>
       <c r="BT6" s="0">
-        <v>0.046637836004409398</v>
+        <v>0.046637836004409399</v>
       </c>
       <c r="BU6" s="0">
         <v>0.020723241114910373</v>
@@ -2269,7 +2270,7 @@
         <v>0.088160098739310591</v>
       </c>
       <c r="CP6" s="0">
-        <v>0.02398369109005876</v>
+        <v>0.023983691090058761</v>
       </c>
       <c r="CQ6" s="0">
         <v>0</v>
@@ -2364,7 +2365,7 @@
         <v>0.37975029369177393</v>
       </c>
       <c r="E7" s="0">
-        <v>0.14640376288820361</v>
+        <v>0.14640376288820362</v>
       </c>
       <c r="F7" s="0">
         <v>0.18650827809818943</v>
@@ -2562,7 +2563,7 @@
         <v>0</v>
       </c>
       <c r="BS7" s="0">
-        <v>0.096934448079486243</v>
+        <v>0.096934448079486244</v>
       </c>
       <c r="BT7" s="0">
         <v>0.093275672008818797</v>
@@ -2810,7 +2811,7 @@
         <v>0.2105263157894737</v>
       </c>
       <c r="AG8" s="0">
-        <v>0.037724460540214277</v>
+        <v>0.037724460540214278</v>
       </c>
       <c r="AH8" s="0">
         <v>0</v>
@@ -2879,7 +2880,7 @@
         <v>0.0084645336041984081</v>
       </c>
       <c r="BD8" s="0">
-        <v>0.068516615279205217</v>
+        <v>0.068516615279205218</v>
       </c>
       <c r="BE8" s="0">
         <v>0.31254883575558684</v>
@@ -2888,7 +2889,7 @@
         <v>0.055532417048452042</v>
       </c>
       <c r="BG8" s="0">
-        <v>0.018484288354898334</v>
+        <v>0.018484288354898335</v>
       </c>
       <c r="BH8" s="0">
         <v>0.055778670236501564</v>
@@ -2984,7 +2985,7 @@
         <v>0.015788808892257169</v>
       </c>
       <c r="CM8" s="0">
-        <v>0.018632383081796162</v>
+        <v>0.018632383081796163</v>
       </c>
       <c r="CN8" s="0">
         <v>0.035893754486719311</v>
@@ -3115,7 +3116,7 @@
         <v>0.27720027720027696</v>
       </c>
       <c r="N9" s="0">
-        <v>0.32191069574247116</v>
+        <v>0.32191069574247117</v>
       </c>
       <c r="O9" s="0">
         <v>0.38889987476105697</v>
@@ -3130,7 +3131,7 @@
         <v>0</v>
       </c>
       <c r="S9" s="0">
-        <v>0.21361567753320312</v>
+        <v>0.21361567753320313</v>
       </c>
       <c r="T9" s="0">
         <v>0.27316806665300802</v>
@@ -3163,7 +3164,7 @@
         <v>0.023640661938534261</v>
       </c>
       <c r="AD9" s="0">
-        <v>0.071377587437544548</v>
+        <v>0.071377587437544549</v>
       </c>
       <c r="AE9" s="0">
         <v>0.068306010928961686</v>
@@ -3289,7 +3290,7 @@
         <v>0.13732380144593873</v>
       </c>
       <c r="BT9" s="0">
-        <v>0.072076655643178097</v>
+        <v>0.072076655643178098</v>
       </c>
       <c r="BU9" s="0">
         <v>0.051808102787275885</v>
@@ -3447,10 +3448,10 @@
         <v>0.38002651347768485</v>
       </c>
       <c r="D10" s="0">
-        <v>0.69120017484905671</v>
+        <v>0.69120017484905672</v>
       </c>
       <c r="E10" s="0">
-        <v>0.32084228888265925</v>
+        <v>0.32084228888265926</v>
       </c>
       <c r="F10" s="0">
         <v>0.39884077931766704</v>
@@ -3468,7 +3469,7 @@
         <v>0.5818786367414801</v>
       </c>
       <c r="K10" s="0">
-        <v>0.45610034207525701</v>
+        <v>0.45610034207525702</v>
       </c>
       <c r="L10" s="0">
         <v>0.31965903036760818</v>
@@ -3489,7 +3490,7 @@
         <v>0.051440329218107039</v>
       </c>
       <c r="R10" s="0">
-        <v>0.18365472910927474</v>
+        <v>0.18365472910927475</v>
       </c>
       <c r="S10" s="0">
         <v>0.31113587814618771</v>
@@ -3588,7 +3589,7 @@
         <v>0.020257267294641969</v>
       </c>
       <c r="AY10" s="0">
-        <v>0.067408156386922879</v>
+        <v>0.06740815638692288</v>
       </c>
       <c r="AZ10" s="0">
         <v>0.043225886130665726</v>
@@ -3845,7 +3846,7 @@
         <v>0.46140663107244045</v>
       </c>
       <c r="P11" s="0">
-        <v>0.29574020360575531</v>
+        <v>0.29574020360575532</v>
       </c>
       <c r="Q11" s="0">
         <v>0.30864197530864168</v>
@@ -3854,7 +3855,7 @@
         <v>0.045913682277318603</v>
       </c>
       <c r="S11" s="0">
-        <v>0.32042351629980464</v>
+        <v>0.32042351629980465</v>
       </c>
       <c r="T11" s="0">
         <v>0.50536092330806481</v>
@@ -3992,7 +3993,7 @@
         <v>0.089160616481976734</v>
       </c>
       <c r="BM11" s="0">
-        <v>0.092705255229155722</v>
+        <v>0.092705255229155723</v>
       </c>
       <c r="BN11" s="0">
         <v>0</v>
@@ -4037,7 +4038,7 @@
         <v>0.30075187969924788</v>
       </c>
       <c r="CB11" s="0">
-        <v>0.052493438320209924</v>
+        <v>0.052493438320209925</v>
       </c>
       <c r="CC11" s="0">
         <v>0.099987501562304626</v>
@@ -4171,7 +4172,7 @@
         <v>0.39475622330240129</v>
       </c>
       <c r="D12" s="0">
-        <v>0.76223260388492819</v>
+        <v>0.7622326038849282</v>
       </c>
       <c r="E12" s="0">
         <v>0.41117652555835937</v>
@@ -4189,7 +4190,7 @@
         <v>0.53709856035437487</v>
       </c>
       <c r="J12" s="0">
-        <v>0.72255259287678308</v>
+        <v>0.72255259287678309</v>
       </c>
       <c r="K12" s="0">
         <v>0.60813378943367602</v>
@@ -4249,7 +4250,7 @@
         <v>0.047281323877068605</v>
       </c>
       <c r="AD12" s="0">
-        <v>0.095170116583392902</v>
+        <v>0.095170116583392903</v>
       </c>
       <c r="AE12" s="0">
         <v>0.2732240437158473</v>
@@ -4261,7 +4262,7 @@
         <v>0.090538705296514352</v>
       </c>
       <c r="AH12" s="0">
-        <v>0.039644782746590584</v>
+        <v>0.039644782746590585</v>
       </c>
       <c r="AI12" s="0">
         <v>0.21283064761325651</v>
@@ -4339,13 +4340,13 @@
         <v>0.030807147258163924</v>
       </c>
       <c r="BH12" s="0">
-        <v>0.094823739402052742</v>
+        <v>0.094823739402052743</v>
       </c>
       <c r="BI12" s="0">
         <v>0.053792361484669225</v>
       </c>
       <c r="BJ12" s="0">
-        <v>0.088446655610834798</v>
+        <v>0.088446655610834799</v>
       </c>
       <c r="BK12" s="0">
         <v>0.0068686036128855071</v>
@@ -4420,7 +4421,7 @@
         <v>0.088335320878053167</v>
       </c>
       <c r="CI12" s="0">
-        <v>0.088740987243483171</v>
+        <v>0.088740987243483172</v>
       </c>
       <c r="CJ12" s="0">
         <v>0.042167404596247141</v>
@@ -4527,7 +4528,7 @@
         <v>0.64806987883910905</v>
       </c>
       <c r="B13" s="0">
-        <v>0.57701956848971347</v>
+        <v>0.57701956848971348</v>
       </c>
       <c r="C13" s="0">
         <v>0.51553984386507534</v>
@@ -4539,7 +4540,7 @@
         <v>0.46724605177086209</v>
       </c>
       <c r="F13" s="0">
-        <v>0.44475050931106674</v>
+        <v>0.44475050931106675</v>
       </c>
       <c r="G13" s="0">
         <v>0.6143162393162388</v>
@@ -4581,7 +4582,7 @@
         <v>0.55725828921705156</v>
       </c>
       <c r="T13" s="0">
-        <v>0.56682373830499166</v>
+        <v>0.56682373830499167</v>
       </c>
       <c r="U13" s="0">
         <v>0.14872652909462714</v>
@@ -4611,7 +4612,7 @@
         <v>0.047281323877068522</v>
       </c>
       <c r="AD13" s="0">
-        <v>0.071377587437544548</v>
+        <v>0.071377587437544549</v>
       </c>
       <c r="AE13" s="0">
         <v>0.068306010928961686</v>
@@ -4668,7 +4669,7 @@
         <v>0.10432968179447044</v>
       </c>
       <c r="AW13" s="0">
-        <v>0.18837459634015052</v>
+        <v>0.18837459634015053</v>
       </c>
       <c r="AX13" s="0">
         <v>0.13167223741517256</v>
@@ -4725,7 +4726,7 @@
         <v>0.056287290329843469</v>
       </c>
       <c r="BP13" s="0">
-        <v>0.27189888300999387</v>
+        <v>0.27189888300999388</v>
       </c>
       <c r="BQ13" s="0">
         <v>0.28715003589375421</v>
@@ -4785,7 +4786,7 @@
         <v>0.21075984470327214</v>
       </c>
       <c r="CJ13" s="0">
-        <v>0.031625553447185296</v>
+        <v>0.031625553447185297</v>
       </c>
       <c r="CK13" s="0">
         <v>0.011352348517099466</v>
@@ -4937,7 +4938,7 @@
         <v>0.61728395061728447</v>
       </c>
       <c r="R14" s="0">
-        <v>0.18365472910927474</v>
+        <v>0.18365472910927475</v>
       </c>
       <c r="S14" s="0">
         <v>0.66406612798365439</v>
@@ -4955,7 +4956,7 @@
         <v>0.10256410256410266</v>
       </c>
       <c r="X14" s="0">
-        <v>0.41690354368012172</v>
+        <v>0.41690354368012173</v>
       </c>
       <c r="Y14" s="0">
         <v>0.15723270440251585</v>
@@ -4973,7 +4974,7 @@
         <v>0.11820330969267151</v>
       </c>
       <c r="AD14" s="0">
-        <v>0.095170116583392902</v>
+        <v>0.095170116583392903</v>
       </c>
       <c r="AE14" s="0">
         <v>0.2732240437158473</v>
@@ -4994,7 +4995,7 @@
         <v>0.051599587203302426</v>
       </c>
       <c r="AK14" s="0">
-        <v>0.037144342916573841</v>
+        <v>0.037144342916573842</v>
       </c>
       <c r="AL14" s="0">
         <v>0.025794802347327037</v>
@@ -5057,7 +5058,7 @@
         <v>0.65635255508673296</v>
       </c>
       <c r="BF14" s="0">
-        <v>0.48590864917395576</v>
+        <v>0.48590864917395577</v>
       </c>
       <c r="BG14" s="0">
         <v>0.055452865064695066</v>
@@ -5266,7 +5267,7 @@
         <v>0.75464118676651959</v>
       </c>
       <c r="G15" s="0">
-        <v>0.85470085470085388</v>
+        <v>0.85470085470085389</v>
       </c>
       <c r="H15" s="0">
         <v>0.82753052780300662</v>
@@ -5281,7 +5282,7 @@
         <v>0.93120486507031464</v>
       </c>
       <c r="L15" s="0">
-        <v>0.58604155567394733</v>
+        <v>0.58604155567394734</v>
       </c>
       <c r="M15" s="0">
         <v>0.62370062370062318</v>
@@ -5311,7 +5312,7 @@
         <v>0.35322550659973939</v>
       </c>
       <c r="V15" s="0">
-        <v>0.68933823529411697</v>
+        <v>0.68933823529411698</v>
       </c>
       <c r="W15" s="0">
         <v>0.10256410256410248</v>
@@ -5374,7 +5375,7 @@
         <v>0</v>
       </c>
       <c r="AQ15" s="0">
-        <v>0.2288984263233188</v>
+        <v>0.22889842632331881</v>
       </c>
       <c r="AR15" s="0">
         <v>0.02492211838006228</v>
@@ -5443,7 +5444,7 @@
         <v>0.24914537342835599</v>
       </c>
       <c r="BN15" s="0">
-        <v>0.031046258925799416</v>
+        <v>0.031046258925799417</v>
       </c>
       <c r="BO15" s="0">
         <v>0.11257458065968694</v>
@@ -5509,7 +5510,7 @@
         <v>0.29950083194675514</v>
       </c>
       <c r="CJ15" s="0">
-        <v>0.031625553447185296</v>
+        <v>0.031625553447185297</v>
       </c>
       <c r="CK15" s="0">
         <v>0.051085568326947592</v>
@@ -5613,7 +5614,7 @@
         <v>0.88556132512176555</v>
       </c>
       <c r="B16" s="0">
-        <v>0.82371634052517217</v>
+        <v>0.82371634052517218</v>
       </c>
       <c r="C16" s="0">
         <v>0.69818824569156057</v>
@@ -5652,7 +5653,7 @@
         <v>0.98650051921080051</v>
       </c>
       <c r="O16" s="0">
-        <v>0.96236240195109179</v>
+        <v>0.9623624019510918</v>
       </c>
       <c r="P16" s="0">
         <v>0.61422965364272364</v>
@@ -5703,7 +5704,7 @@
         <v>0.47814207650273272</v>
       </c>
       <c r="AF16" s="0">
-        <v>0.28070175438596517</v>
+        <v>0.28070175438596518</v>
       </c>
       <c r="AG16" s="0">
         <v>0.23389165534932871</v>
@@ -5787,7 +5788,7 @@
         <v>0.098582871226124552</v>
       </c>
       <c r="BH16" s="0">
-        <v>0.25658188308790741</v>
+        <v>0.25658188308790742</v>
       </c>
       <c r="BI16" s="0">
         <v>0.13986013986013998</v>
@@ -5999,7 +6000,7 @@
         <v>0.86378737541528161</v>
       </c>
       <c r="J17" s="0">
-        <v>1.0102947758808098</v>
+        <v>1.0102947758808099</v>
       </c>
       <c r="K17" s="0">
         <v>1.0452299505891287</v>
@@ -6370,7 +6371,7 @@
         <v>0.94121825608240017</v>
       </c>
       <c r="M18" s="0">
-        <v>0.49896049896049854</v>
+        <v>0.49896049896049855</v>
       </c>
       <c r="N18" s="0">
         <v>1.0280373831775691</v>
@@ -6406,7 +6407,7 @@
         <v>0.89065757058934913</v>
       </c>
       <c r="Y18" s="0">
-        <v>0.44549266247379415</v>
+        <v>0.44549266247379416</v>
       </c>
       <c r="Z18" s="0">
         <v>0.045756119881034049</v>
@@ -6451,10 +6452,10 @@
         <v>0.64874884151992529</v>
       </c>
       <c r="AN18" s="0">
-        <v>0.21729682746631881</v>
+        <v>0.21729682746631882</v>
       </c>
       <c r="AO18" s="0">
-        <v>0.089887640449438116</v>
+        <v>0.089887640449438117</v>
       </c>
       <c r="AP18" s="0">
         <v>0.0883002207505518</v>
@@ -6529,7 +6530,7 @@
         <v>0.32446839330204502</v>
       </c>
       <c r="BN18" s="0">
-        <v>0.031046258925799416</v>
+        <v>0.031046258925799417</v>
       </c>
       <c r="BO18" s="0">
         <v>0.24766407745131128</v>
@@ -6696,7 +6697,7 @@
     </row>
     <row r="19">
       <c r="A19" s="0">
-        <v>1.0586483113955671</v>
+        <v>1.0586483113955672</v>
       </c>
       <c r="B19" s="0">
         <v>1.0244187991302922</v>
@@ -6711,13 +6712,13 @@
         <v>1.0217113665389557</v>
       </c>
       <c r="F19" s="0">
-        <v>1.1219190267137273</v>
+        <v>1.1219190267137274</v>
       </c>
       <c r="G19" s="0">
         <v>1.1618589743589776</v>
       </c>
       <c r="H19" s="0">
-        <v>0.97890806337673097</v>
+        <v>0.97890806337673098</v>
       </c>
       <c r="I19" s="0">
         <v>1.079734219269106</v>
@@ -6786,7 +6787,7 @@
         <v>0.4996431120628137</v>
       </c>
       <c r="AE19" s="0">
-        <v>0.54644808743169559</v>
+        <v>0.5464480874316956</v>
       </c>
       <c r="AF19" s="0">
         <v>0.42105263157894857</v>
@@ -6825,7 +6826,7 @@
         <v>0.40057224606580943</v>
       </c>
       <c r="AR19" s="0">
-        <v>0.14953271028037426</v>
+        <v>0.14953271028037427</v>
       </c>
       <c r="AS19" s="0">
         <v>0.66137566137566317</v>
@@ -6876,7 +6877,7 @@
         <v>0.53547523427041643</v>
       </c>
       <c r="BI19" s="0">
-        <v>0.28330643715259179</v>
+        <v>0.2833064371525918</v>
       </c>
       <c r="BJ19" s="0">
         <v>0.29850746268656803</v>
@@ -6912,7 +6913,7 @@
         <v>0.61477147460358006</v>
       </c>
       <c r="BU19" s="0">
-        <v>0.23831727282146994</v>
+        <v>0.23831727282146995</v>
       </c>
       <c r="BV19" s="0">
         <v>0.85176085176085414</v>
@@ -6939,7 +6940,7 @@
         <v>0.38745156855393187</v>
       </c>
       <c r="CD19" s="0">
-        <v>0.5256410256410271</v>
+        <v>0.52564102564102711</v>
       </c>
       <c r="CE19" s="0">
         <v>0.69841269841270037</v>
@@ -7103,7 +7104,7 @@
         <v>1.2853470437017984</v>
       </c>
       <c r="P20" s="0">
-        <v>0.81897287152363007</v>
+        <v>0.81897287152363008</v>
       </c>
       <c r="Q20" s="0">
         <v>1.0802469135802459</v>
@@ -7226,7 +7227,7 @@
         <v>0.47276464542651553</v>
       </c>
       <c r="BE20" s="0">
-        <v>1.2970776683856839</v>
+        <v>1.297077668385684</v>
       </c>
       <c r="BF20" s="0">
         <v>0.70803831736776279</v>
@@ -7423,7 +7424,7 @@
         <v>1.1190274926538653</v>
       </c>
       <c r="B21" s="0">
-        <v>1.0829570162234476</v>
+        <v>1.0829570162234477</v>
       </c>
       <c r="C21" s="0">
         <v>1.1194579466784496</v>
@@ -7549,7 +7550,7 @@
         <v>0.4721030042918451</v>
       </c>
       <c r="AR21" s="0">
-        <v>0.2367601246105917</v>
+        <v>0.23676012461059171</v>
       </c>
       <c r="AS21" s="0">
         <v>1.0582010582010573</v>
@@ -7585,13 +7586,13 @@
         <v>0.38513627899102726</v>
       </c>
       <c r="BD21" s="0">
-        <v>0.54813292223364118</v>
+        <v>0.54813292223364119</v>
       </c>
       <c r="BE21" s="0">
         <v>1.4533520862634774</v>
       </c>
       <c r="BF21" s="0">
-        <v>1.0134666111342487</v>
+        <v>1.0134666111342488</v>
       </c>
       <c r="BG21" s="0">
         <v>0.30191004313000591</v>
@@ -7627,7 +7628,7 @@
         <v>0.76573342905001129</v>
       </c>
       <c r="BR21" s="0">
-        <v>0.17760555421005877</v>
+        <v>0.17760555421005878</v>
       </c>
       <c r="BS21" s="0">
         <v>1.1066682822408003</v>
@@ -7699,7 +7700,7 @@
         <v>0.93449704663669131</v>
       </c>
       <c r="CP21" s="0">
-        <v>0.38373905744093983</v>
+        <v>0.38373905744093984</v>
       </c>
       <c r="CQ21" s="0">
         <v>0</v>
@@ -7938,16 +7939,16 @@
         <v>0.56193651969865333</v>
       </c>
       <c r="BA22" s="0">
-        <v>0.80738177623990703</v>
+        <v>0.80738177623990704</v>
       </c>
       <c r="BB22" s="0">
         <v>0.32525133057362482</v>
       </c>
       <c r="BC22" s="0">
-        <v>0.52480108346030085</v>
+        <v>0.52480108346030086</v>
       </c>
       <c r="BD22" s="0">
-        <v>0.71257279890373348</v>
+        <v>0.71257279890373349</v>
       </c>
       <c r="BE22" s="0">
         <v>1.3283325519612428</v>
@@ -7971,7 +7972,7 @@
         <v>0.22666391922522131</v>
       </c>
       <c r="BL22" s="0">
-        <v>0.40759138963189367</v>
+        <v>0.40759138963189368</v>
       </c>
       <c r="BM22" s="0">
         <v>0.59679008053768989</v>
@@ -8010,7 +8011,7 @@
         <v>0.50483803113167813</v>
       </c>
       <c r="BY22" s="0">
-        <v>0.83612040133779197</v>
+        <v>0.83612040133779198</v>
       </c>
       <c r="BZ22" s="0">
         <v>0.84254870984728725</v>
@@ -8025,7 +8026,7 @@
         <v>0.69991251093613238</v>
       </c>
       <c r="CD22" s="0">
-        <v>0.64102564102564052</v>
+        <v>0.64102564102564053</v>
       </c>
       <c r="CE22" s="0">
         <v>0.69841269841269771</v>
@@ -8130,7 +8131,7 @@
         <v>0.47867711053089601</v>
       </c>
       <c r="DM22" s="0">
-        <v>0.64102564102564052</v>
+        <v>0.64102564102564053</v>
       </c>
       <c r="DN22" s="0">
         <v>0</v>
@@ -8327,7 +8328,7 @@
         <v>0.44826967903891107</v>
       </c>
       <c r="BJ23" s="0">
-        <v>0.57121798415330904</v>
+        <v>0.57121798415330905</v>
       </c>
       <c r="BK23" s="0">
         <v>0.26100693728964974</v>
@@ -8450,7 +8451,7 @@
         <v>0.1597954618088851</v>
       </c>
       <c r="CY23" s="0">
-        <v>0.040521922359996874</v>
+        <v>0.040521922359996875</v>
       </c>
       <c r="CZ23" s="0">
         <v>0</v>
@@ -8459,13 +8460,13 @@
         <v>0.024015369836695551</v>
       </c>
       <c r="DB23" s="0">
-        <v>0.26123301985371022</v>
+        <v>0.26123301985371023</v>
       </c>
       <c r="DC23" s="0">
         <v>0.044903457566232728</v>
       </c>
       <c r="DD23" s="0">
-        <v>0.006071645415907728</v>
+        <v>0.0060716454159077281</v>
       </c>
       <c r="DE23" s="0">
         <v>0.59610117609151125</v>
@@ -8545,7 +8546,7 @@
         <v>1.2196812196812186</v>
       </c>
       <c r="N24" s="0">
-        <v>1.3187954309449625</v>
+        <v>1.3187954309449626</v>
       </c>
       <c r="O24" s="0">
         <v>1.4501351262276698</v>
@@ -8752,7 +8753,7 @@
         <v>0.75641025641025572</v>
       </c>
       <c r="CE24" s="0">
-        <v>0.82539682539682468</v>
+        <v>0.82539682539682469</v>
       </c>
       <c r="CF24" s="0">
         <v>0.28785261945883683</v>
@@ -8770,7 +8771,7 @@
         <v>0.35842293906810008</v>
       </c>
       <c r="CK24" s="0">
-        <v>0.22420888321271445</v>
+        <v>0.22420888321271446</v>
       </c>
       <c r="CL24" s="0">
         <v>0.48629531388152036</v>
@@ -8860,7 +8861,7 @@
         <v>0</v>
       </c>
       <c r="DO24" s="0">
-        <v>0.40453074433656921</v>
+        <v>0.40453074433656922</v>
       </c>
       <c r="DP24" s="0">
         <v>0</v>
@@ -8907,7 +8908,7 @@
         <v>1.3444213444213433</v>
       </c>
       <c r="N25" s="0">
-        <v>1.4849428868120444</v>
+        <v>1.4849428868120445</v>
       </c>
       <c r="O25" s="0">
         <v>1.344670753411112</v>
@@ -8931,7 +8932,7 @@
         <v>1.2269938650306738</v>
       </c>
       <c r="V25" s="0">
-        <v>1.2254901960784303</v>
+        <v>1.2254901960784304</v>
       </c>
       <c r="W25" s="0">
         <v>0.61538461538461486</v>
@@ -9009,7 +9010,7 @@
         <v>1.4404055390702262</v>
       </c>
       <c r="AV25" s="0">
-        <v>0.96132349653476334</v>
+        <v>0.96132349653476335</v>
       </c>
       <c r="AW25" s="0">
         <v>0.98672407606745516</v>
@@ -9078,7 +9079,7 @@
         <v>0.46015984499878859</v>
       </c>
       <c r="BS25" s="0">
-        <v>1.0783957348842836</v>
+        <v>1.0783957348842837</v>
       </c>
       <c r="BT25" s="0">
         <v>1.0853896379207995</v>
@@ -9239,7 +9240,7 @@
         <v>1.3728089556635721</v>
       </c>
       <c r="D26" s="0">
-        <v>1.2867797721498226</v>
+        <v>1.2867797721498227</v>
       </c>
       <c r="E26" s="0">
         <v>1.3114039186368864</v>
@@ -9266,7 +9267,7 @@
         <v>1.4562244716746569</v>
       </c>
       <c r="M26" s="0">
-        <v>1.2612612612612601</v>
+        <v>1.2612612612612602</v>
       </c>
       <c r="N26" s="0">
         <v>1.2876427829698847</v>
@@ -9359,7 +9360,7 @@
         <v>0.95851216022889763</v>
       </c>
       <c r="AR26" s="0">
-        <v>0.41121495327102769</v>
+        <v>0.4112149532710277</v>
       </c>
       <c r="AS26" s="0">
         <v>1.3888888888888875</v>
@@ -9458,7 +9459,7 @@
         <v>1.0938157341186361</v>
       </c>
       <c r="BY26" s="0">
-        <v>1.282051282051281</v>
+        <v>1.2820512820512811</v>
       </c>
       <c r="BZ26" s="0">
         <v>0.96103212216956213</v>
@@ -9509,7 +9510,7 @@
         <v>1.3400335008375197</v>
       </c>
       <c r="CP26" s="0">
-        <v>0.74749170564016409</v>
+        <v>0.7474917056401641</v>
       </c>
       <c r="CQ26" s="0">
         <v>0.043346337234503644</v>
@@ -9694,7 +9695,7 @@
         <v>0.40437678401522326</v>
       </c>
       <c r="AI27" s="0">
-        <v>1.3175230566534903</v>
+        <v>1.3175230566534904</v>
       </c>
       <c r="AJ27" s="0">
         <v>0.61919504643962786</v>
@@ -9772,7 +9773,7 @@
         <v>1.0486390004462285</v>
       </c>
       <c r="BI27" s="0">
-        <v>0.79254079254079179</v>
+        <v>0.7925407925407918</v>
       </c>
       <c r="BJ27" s="0">
         <v>0.90289294269393694</v>
@@ -9934,7 +9935,7 @@
         <v>2.5067750677506755</v>
       </c>
       <c r="DK27" s="0">
-        <v>3.582986592695327</v>
+        <v>3.5829865926953271</v>
       </c>
       <c r="DL27" s="0">
         <v>2.8285465622280217</v>
@@ -9975,7 +9976,7 @@
         <v>1.4289529914529955</v>
       </c>
       <c r="H28" s="0">
-        <v>1.3523059844585767</v>
+        <v>1.3523059844585768</v>
       </c>
       <c r="I28" s="0">
         <v>1.290143964562573</v>
@@ -10059,7 +10060,7 @@
         <v>1.2871186784230297</v>
       </c>
       <c r="AJ28" s="0">
-        <v>0.38183694530443862</v>
+        <v>0.38183694530443863</v>
       </c>
       <c r="AK28" s="0">
         <v>0.4828764579154608</v>
@@ -10083,7 +10084,7 @@
         <v>1.2446351931330508</v>
       </c>
       <c r="AR28" s="0">
-        <v>0.67289719626168409</v>
+        <v>0.6728971962616841</v>
       </c>
       <c r="AS28" s="0">
         <v>1.6534391534391579</v>
@@ -10092,7 +10093,7 @@
         <v>0.94602114635503887</v>
       </c>
       <c r="AU28" s="0">
-        <v>1.4527695351137528</v>
+        <v>1.4527695351137529</v>
       </c>
       <c r="AV28" s="0">
         <v>1.1401743796110027</v>
@@ -10107,7 +10108,7 @@
         <v>0.78867542972699922</v>
       </c>
       <c r="AZ28" s="0">
-        <v>1.1670989255279764</v>
+        <v>1.1670989255279765</v>
       </c>
       <c r="BA28" s="0">
         <v>1.4574813882772402</v>
@@ -10119,7 +10120,7 @@
         <v>0.90147282884713309</v>
       </c>
       <c r="BD28" s="0">
-        <v>1.2195957519698561</v>
+        <v>1.2195957519698562</v>
       </c>
       <c r="BE28" s="0">
         <v>1.2345679012345714</v>
@@ -10532,7 +10533,7 @@
         <v>1.2846603917578212</v>
       </c>
       <c r="BU29" s="0">
-        <v>1.1397782613200695</v>
+        <v>1.1397782613200696</v>
       </c>
       <c r="BV29" s="0">
         <v>1.4250614250614237</v>
@@ -10756,7 +10757,7 @@
         <v>0.45756119881034046</v>
       </c>
       <c r="AA30" s="0">
-        <v>0.23453532688361164</v>
+        <v>0.23453532688361165</v>
       </c>
       <c r="AB30" s="0">
         <v>1.1240547721234406</v>
@@ -10831,7 +10832,7 @@
         <v>1.1391978429389946</v>
       </c>
       <c r="AZ30" s="0">
-        <v>1.2659009509694938</v>
+        <v>1.2659009509694939</v>
       </c>
       <c r="BA30" s="0">
         <v>1.4679668658907399</v>
@@ -11073,7 +11074,7 @@
         <v>1.2352717597871521</v>
       </c>
       <c r="L31" s="0">
-        <v>1.1188066062866266</v>
+        <v>1.1188066062866267</v>
       </c>
       <c r="M31" s="0">
         <v>1.2335412335412326</v>
@@ -11127,13 +11128,13 @@
         <v>1.182033096926713</v>
       </c>
       <c r="AD31" s="0">
-        <v>1.4513442778967391</v>
+        <v>1.4513442778967392</v>
       </c>
       <c r="AE31" s="0">
         <v>1.2295081967213104</v>
       </c>
       <c r="AF31" s="0">
-        <v>2.1052631578947349</v>
+        <v>2.105263157894735</v>
       </c>
       <c r="AG31" s="0">
         <v>1.1694582767466415</v>
@@ -11241,7 +11242,7 @@
         <v>1.0244286840031511</v>
       </c>
       <c r="BP31" s="0">
-        <v>1.2492651381540258</v>
+        <v>1.2492651381540259</v>
       </c>
       <c r="BQ31" s="0">
         <v>1.1605647284039236</v>
@@ -11549,7 +11550,7 @@
         <v>1.4442052386078261</v>
       </c>
       <c r="AX32" s="0">
-        <v>1.2762078395624465</v>
+        <v>1.2762078395624466</v>
       </c>
       <c r="AY32" s="0">
         <v>1.1998651836872296</v>
@@ -11561,7 +11562,7 @@
         <v>1.4365104330502294</v>
       </c>
       <c r="BB32" s="0">
-        <v>1.1038833037650337</v>
+        <v>1.1038833037650338</v>
       </c>
       <c r="BC32" s="0">
         <v>1.252750973421368</v>
@@ -11576,7 +11577,7 @@
         <v>1.3605442176870786</v>
       </c>
       <c r="BG32" s="0">
-        <v>0.967344423906349</v>
+        <v>0.96734442390634901</v>
       </c>
       <c r="BH32" s="0">
         <v>1.4167782240071436</v>
@@ -11696,7 +11697,7 @@
         <v>2.3227873448137828</v>
       </c>
       <c r="CU32" s="0">
-        <v>2.7944111776447182</v>
+        <v>2.7944111776447183</v>
       </c>
       <c r="CV32" s="0">
         <v>1.2437810945273666</v>
@@ -11714,7 +11715,7 @@
         <v>0.41948263807970287</v>
       </c>
       <c r="DA32" s="0">
-        <v>2.8578290105667707</v>
+        <v>2.8578290105667708</v>
       </c>
       <c r="DB32" s="0">
         <v>4.0752351097178794</v>
@@ -11764,7 +11765,7 @@
     </row>
     <row r="33">
       <c r="A33" s="0">
-        <v>1.1351286076560791</v>
+        <v>1.1351286076560792</v>
       </c>
       <c r="B33" s="0">
         <v>0.89479846128114993</v>
@@ -11815,7 +11816,7 @@
         <v>1.2345679012345667</v>
       </c>
       <c r="R33" s="0">
-        <v>1.377410468319558</v>
+        <v>1.3774104683195581</v>
       </c>
       <c r="S33" s="0">
         <v>1.2584749698151749</v>
@@ -11839,7 +11840,7 @@
         <v>1.3102725366876298</v>
       </c>
       <c r="Z33" s="0">
-        <v>0.75497597803706173</v>
+        <v>0.75497597803706174</v>
       </c>
       <c r="AA33" s="0">
         <v>0.41043682204632037</v>
@@ -11863,7 +11864,7 @@
         <v>1.2524520899351128</v>
       </c>
       <c r="AH33" s="0">
-        <v>0.9118300031715818</v>
+        <v>0.91183000317158181</v>
       </c>
       <c r="AI33" s="0">
         <v>1.2364447147055833</v>
@@ -11917,7 +11918,7 @@
         <v>1.2807549713515325</v>
       </c>
       <c r="AZ33" s="0">
-        <v>1.2659009509694938</v>
+        <v>1.2659009509694939</v>
       </c>
       <c r="BA33" s="0">
         <v>1.1638880150990867</v>
@@ -11983,7 +11984,7 @@
         <v>1.4713501191586351</v>
       </c>
       <c r="BV33" s="0">
-        <v>1.4905814905814891</v>
+        <v>1.4905814905814892</v>
       </c>
       <c r="BW33" s="0">
         <v>0.62865497076023336</v>
@@ -12061,7 +12062,7 @@
         <v>2.3952095808383214</v>
       </c>
       <c r="CV33" s="0">
-        <v>2.1144278606965154</v>
+        <v>2.1144278606965155</v>
       </c>
       <c r="CW33" s="0">
         <v>4.3077296444606201</v>
@@ -12112,7 +12113,7 @@
         <v>1.914708442123584</v>
       </c>
       <c r="DM33" s="0">
-        <v>1.282051282051281</v>
+        <v>1.2820512820512811</v>
       </c>
       <c r="DN33" s="0">
         <v>2.7343749999999978</v>
@@ -12132,7 +12133,7 @@
         <v>0.86134805151363025</v>
       </c>
       <c r="C34" s="0">
-        <v>1.1135660627485628</v>
+        <v>1.1135660627485629</v>
       </c>
       <c r="D34" s="0">
         <v>0.71578832336147247</v>
@@ -12144,7 +12145,7 @@
         <v>1.0272302086023348</v>
       </c>
       <c r="G34" s="0">
-        <v>0.85470085470085388</v>
+        <v>0.85470085470085389</v>
       </c>
       <c r="H34" s="0">
         <v>0.99909173478655677</v>
@@ -12168,7 +12169,7 @@
         <v>0.6749740394600201</v>
       </c>
       <c r="O34" s="0">
-        <v>0.87667259903763683</v>
+        <v>0.87667259903763684</v>
       </c>
       <c r="P34" s="0">
         <v>1.1715861912074153</v>
@@ -12255,7 +12256,7 @@
         <v>1.2875536480686685</v>
       </c>
       <c r="AR34" s="0">
-        <v>1.3084112149532698</v>
+        <v>1.3084112149532699</v>
       </c>
       <c r="AS34" s="0">
         <v>1.1904761904761894</v>
@@ -12282,7 +12283,7 @@
         <v>1.3029517105100643</v>
       </c>
       <c r="BA34" s="0">
-        <v>1.3421411345286764</v>
+        <v>1.3421411345286765</v>
       </c>
       <c r="BB34" s="0">
         <v>1.13345160654445</v>
@@ -12414,7 +12415,7 @@
         <v>3.8617236603813749</v>
       </c>
       <c r="CS34" s="0">
-        <v>2.565236620964173</v>
+        <v>2.5652366209641731</v>
       </c>
       <c r="CT34" s="0">
         <v>3.504205046055263</v>
@@ -12438,7 +12439,7 @@
         <v>1.087547580206633</v>
       </c>
       <c r="DA34" s="0">
-        <v>4.0826128722382284</v>
+        <v>4.0826128722382285</v>
       </c>
       <c r="DB34" s="0">
         <v>2.6384535005224636</v>
@@ -12474,7 +12475,7 @@
         <v>1.3925152306353339</v>
       </c>
       <c r="DM34" s="0">
-        <v>0.64102564102564052</v>
+        <v>0.64102564102564053</v>
       </c>
       <c r="DN34" s="0">
         <v>4.8177083333333295</v>
@@ -12533,7 +12534,7 @@
         <v>0.79098279612418365</v>
       </c>
       <c r="P35" s="0">
-        <v>1.1886481260308241</v>
+        <v>1.1886481260308242</v>
       </c>
       <c r="Q35" s="0">
         <v>0.72016460905349722</v>
@@ -12662,7 +12663,7 @@
         <v>1.0689990281827007</v>
       </c>
       <c r="BG35" s="0">
-        <v>1.2014787430683906</v>
+        <v>1.2014787430683907</v>
       </c>
       <c r="BH35" s="0">
         <v>1.4390896921017391</v>
@@ -12692,7 +12693,7 @@
         <v>1.3007054673721328</v>
       </c>
       <c r="BQ35" s="0">
-        <v>0.93323761665470117</v>
+        <v>0.93323761665470118</v>
       </c>
       <c r="BR35" s="0">
         <v>1.2270929199967697</v>
@@ -12821,7 +12822,7 @@
         <v>4.3699186991869885</v>
       </c>
       <c r="DH35" s="0">
-        <v>2.7629233511586428</v>
+        <v>2.7629233511586429</v>
       </c>
       <c r="DI35" s="0">
         <v>0.62305295950155704</v>
@@ -12877,7 +12878,7 @@
         <v>0.86378737541528161</v>
       </c>
       <c r="J36" s="0">
-        <v>0.70336978067651323</v>
+        <v>0.70336978067651324</v>
       </c>
       <c r="K36" s="0">
         <v>0.53211706575446549</v>
@@ -12913,7 +12914,7 @@
         <v>1.2269938650306738</v>
       </c>
       <c r="V36" s="0">
-        <v>1.2254901960784303</v>
+        <v>1.2254901960784304</v>
       </c>
       <c r="W36" s="0">
         <v>1.2307692307692297</v>
@@ -12943,7 +12944,7 @@
         <v>1.2978142076502721</v>
       </c>
       <c r="AF36" s="0">
-        <v>1.3333333333333321</v>
+        <v>1.3333333333333322</v>
       </c>
       <c r="AG36" s="0">
         <v>1.3429907952316269</v>
@@ -13000,7 +13001,7 @@
         <v>1.4990377798035031</v>
       </c>
       <c r="AY36" s="0">
-        <v>1.4492753623188392</v>
+        <v>1.4492753623188393</v>
       </c>
       <c r="AZ36" s="0">
         <v>1.1979745584784476</v>
@@ -13024,7 +13025,7 @@
         <v>1.0412328196584748</v>
       </c>
       <c r="BG36" s="0">
-        <v>1.2076401725200236</v>
+        <v>1.2076401725200237</v>
       </c>
       <c r="BH36" s="0">
         <v>1.3052208835341355</v>
@@ -13036,7 +13037,7 @@
         <v>1.3524967753823463</v>
       </c>
       <c r="BK36" s="0">
-        <v>1.0989765780616791</v>
+        <v>1.0989765780616792</v>
       </c>
       <c r="BL36" s="0">
         <v>1.3756209400076411</v>
@@ -13066,7 +13067,7 @@
         <v>1.4542525226829461</v>
       </c>
       <c r="BU36" s="0">
-        <v>1.2744793285669866</v>
+        <v>1.2744793285669867</v>
       </c>
       <c r="BV36" s="0">
         <v>1.0647010647010637</v>
@@ -13111,7 +13112,7 @@
         <v>1.1647254575707144</v>
       </c>
       <c r="CJ36" s="0">
-        <v>1.3388150959308442</v>
+        <v>1.3388150959308443</v>
       </c>
       <c r="CK36" s="0">
         <v>1.1096920675464725</v>
@@ -13171,7 +13172,7 @@
         <v>3.262984583146233</v>
       </c>
       <c r="DD36" s="0">
-        <v>4.0194292653309009</v>
+        <v>4.019429265330901</v>
       </c>
       <c r="DE36" s="0">
         <v>0.66054454647978034</v>
@@ -13236,7 +13237,7 @@
         <v>0.71652033504894475</v>
       </c>
       <c r="I37" s="0">
-        <v>0.76965669988925733</v>
+        <v>0.76965669988925734</v>
       </c>
       <c r="J37" s="0">
         <v>0.48596457574013641</v>
@@ -13311,7 +13312,7 @@
         <v>1.3580805794477127</v>
       </c>
       <c r="AH37" s="0">
-        <v>1.2607040913415783</v>
+        <v>1.2607040913415784</v>
       </c>
       <c r="AI37" s="0">
         <v>1.1148272017837224</v>
@@ -13583,7 +13584,7 @@
         <v>0.74237737516571412</v>
       </c>
       <c r="D38" s="0">
-        <v>0.45078272272764824</v>
+        <v>0.45078272272764825</v>
       </c>
       <c r="E38" s="0">
         <v>0.68840918294240872</v>
@@ -13595,7 +13596,7 @@
         <v>0.5876068376068414</v>
       </c>
       <c r="H38" s="0">
-        <v>0.65596932081946135</v>
+        <v>0.65596932081946136</v>
       </c>
       <c r="I38" s="0">
         <v>0.62015503875969391</v>
@@ -13628,7 +13629,7 @@
         <v>0.82644628099174089</v>
       </c>
       <c r="S38" s="0">
-        <v>0.65013467075323172</v>
+        <v>0.65013467075323173</v>
       </c>
       <c r="T38" s="0">
         <v>0.6760909649661998</v>
@@ -13760,7 +13761,7 @@
         <v>1.4188317670904829</v>
       </c>
       <c r="BK38" s="0">
-        <v>1.3119032900611391</v>
+        <v>1.3119032900611392</v>
       </c>
       <c r="BL38" s="0">
         <v>1.3183034008406658</v>
@@ -13811,7 +13812,7 @@
         <v>0.85213032581454196</v>
       </c>
       <c r="CB38" s="0">
-        <v>1.1548556430446268</v>
+        <v>1.1548556430446269</v>
       </c>
       <c r="CC38" s="0">
         <v>1.2498437695288172</v>
@@ -13856,7 +13857,7 @@
         <v>1.4670024383419371</v>
       </c>
       <c r="CQ38" s="0">
-        <v>3.1371911573472246</v>
+        <v>3.1371911573472247</v>
       </c>
       <c r="CR38" s="0">
         <v>1.1771599019921244</v>
@@ -13972,7 +13973,7 @@
         <v>0.49724738057183404</v>
       </c>
       <c r="M39" s="0">
-        <v>0.91476091476091403</v>
+        <v>0.91476091476091404</v>
       </c>
       <c r="N39" s="0">
         <v>0.47767393561786042</v>
@@ -13981,7 +13982,7 @@
         <v>0.5602794805879634</v>
       </c>
       <c r="P39" s="0">
-        <v>0.79622362509241817</v>
+        <v>0.79622362509241818</v>
       </c>
       <c r="Q39" s="0">
         <v>0.72016460905349722</v>
@@ -14002,10 +14003,10 @@
         <v>0.91911764705882271</v>
       </c>
       <c r="W39" s="0">
-        <v>1.3333333333333321</v>
+        <v>1.3333333333333322</v>
       </c>
       <c r="X39" s="0">
-        <v>0.73905628197839623</v>
+        <v>0.73905628197839624</v>
       </c>
       <c r="Y39" s="0">
         <v>0.70754716981132004</v>
@@ -14086,7 +14087,7 @@
         <v>1.2964651068570838</v>
       </c>
       <c r="AY39" s="0">
-        <v>1.300977418267609</v>
+        <v>1.3009774182676091</v>
       </c>
       <c r="AZ39" s="0">
         <v>1.284426330739779</v>
@@ -14116,7 +14117,7 @@
         <v>1.2494422132976339</v>
       </c>
       <c r="BI39" s="0">
-        <v>1.380670611439841</v>
+        <v>1.3806706114398411</v>
       </c>
       <c r="BJ39" s="0">
         <v>1.2124562373318581</v>
@@ -14146,7 +14147,7 @@
         <v>1.2351658997335906</v>
       </c>
       <c r="BS39" s="0">
-        <v>0.86837109737873019</v>
+        <v>0.8683710973787302</v>
       </c>
       <c r="BT39" s="0">
         <v>0.99635376918510887</v>
@@ -14224,7 +14225,7 @@
         <v>0.75636518589538648</v>
       </c>
       <c r="CS39" s="0">
-        <v>0.25062656641603986</v>
+        <v>0.25062656641603987</v>
       </c>
       <c r="CT39" s="0">
         <v>2.5830997196635939</v>
@@ -14248,7 +14249,7 @@
         <v>4.2103627747999646</v>
       </c>
       <c r="DA39" s="0">
-        <v>1.9452449567723324</v>
+        <v>1.9452449567723325</v>
       </c>
       <c r="DB39" s="0">
         <v>0.23510971786833837</v>
@@ -14355,7 +14356,7 @@
         <v>0.5340391938330078</v>
       </c>
       <c r="T40" s="0">
-        <v>0.49853172164173964</v>
+        <v>0.49853172164173965</v>
       </c>
       <c r="U40" s="0">
         <v>0.70645101319947878</v>
@@ -14598,7 +14599,7 @@
         <v>2.6119402985074607</v>
       </c>
       <c r="CW40" s="0">
-        <v>0.76447033127047614</v>
+        <v>0.76447033127047615</v>
       </c>
       <c r="CX40" s="0">
         <v>0.095877277085330698</v>
@@ -14663,10 +14664,10 @@
         <v>0.38642676005313337</v>
       </c>
       <c r="B41" s="0">
-        <v>0.34704800133801605</v>
+        <v>0.34704800133801606</v>
       </c>
       <c r="C41" s="0">
-        <v>0.50964795993518885</v>
+        <v>0.50964795993518886</v>
       </c>
       <c r="D41" s="0">
         <v>0.26227358413244795</v>
@@ -14726,7 +14727,7 @@
         <v>0.67401960784313664</v>
       </c>
       <c r="W41" s="0">
-        <v>1.282051282051281</v>
+        <v>1.2820512820512811</v>
       </c>
       <c r="X41" s="0">
         <v>0.66325563767291962</v>
@@ -14921,7 +14922,7 @@
         <v>1.0981697171381022</v>
       </c>
       <c r="CJ41" s="0">
-        <v>1.3388150959308442</v>
+        <v>1.3388150959308443</v>
       </c>
       <c r="CK41" s="0">
         <v>1.3225486022420876</v>
@@ -15022,7 +15023,7 @@
     </row>
     <row r="42">
       <c r="A42" s="0">
-        <v>0.34617397254759857</v>
+        <v>0.34617397254759858</v>
       </c>
       <c r="B42" s="0">
         <v>0.27596588058203692</v>
@@ -15256,7 +15257,7 @@
         <v>0.59241706161137386</v>
       </c>
       <c r="CA42" s="0">
-        <v>0.25062656641603986</v>
+        <v>0.25062656641603987</v>
       </c>
       <c r="CB42" s="0">
         <v>1.3648293963254581</v>
@@ -15283,7 +15284,7 @@
         <v>0.8652246256239593</v>
       </c>
       <c r="CJ42" s="0">
-        <v>1.3388150959308442</v>
+        <v>1.3388150959308443</v>
       </c>
       <c r="CK42" s="0">
         <v>1.2941677309493391</v>
@@ -15310,7 +15311,7 @@
         <v>0.090550761691701204</v>
       </c>
       <c r="CS42" s="0">
-        <v>0.04422821760283057</v>
+        <v>0.044228217602830571</v>
       </c>
       <c r="CT42" s="0">
         <v>0.55399813109064167</v>
@@ -15396,7 +15397,7 @@
         <v>0.16665300658415963</v>
       </c>
       <c r="E43" s="0">
-        <v>0.32395726256113105</v>
+        <v>0.32395726256113106</v>
       </c>
       <c r="F43" s="0">
         <v>0.28980517058334021</v>
@@ -15420,7 +15421,7 @@
         <v>0.30190019534718493</v>
       </c>
       <c r="M43" s="0">
-        <v>0.44352044352044317</v>
+        <v>0.44352044352044318</v>
       </c>
       <c r="N43" s="0">
         <v>0.24922118380062283</v>
@@ -15456,7 +15457,7 @@
         <v>0.41690354368012095</v>
       </c>
       <c r="Y43" s="0">
-        <v>0.68134171907756746</v>
+        <v>0.68134171907756747</v>
       </c>
       <c r="Z43" s="0">
         <v>1.4184397163120555</v>
@@ -15549,7 +15550,7 @@
         <v>1.1257829693583874</v>
       </c>
       <c r="BD43" s="0">
-        <v>0.79479273723877963</v>
+        <v>0.79479273723877964</v>
       </c>
       <c r="BE43" s="0">
         <v>0.21878418502891056</v>
@@ -15588,7 +15589,7 @@
         <v>0.55849500293944687</v>
       </c>
       <c r="BQ43" s="0">
-        <v>0.58626465661641491</v>
+        <v>0.58626465661641492</v>
       </c>
       <c r="BR43" s="0">
         <v>1.2270929199967697</v>
@@ -15627,7 +15628,7 @@
         <v>0.79990001249843701</v>
       </c>
       <c r="CD43" s="0">
-        <v>0.8846153846153838</v>
+        <v>0.88461538461538381</v>
       </c>
       <c r="CE43" s="0">
         <v>1.0158730158730149</v>
@@ -15681,7 +15682,7 @@
         <v>0</v>
       </c>
       <c r="CV43" s="0">
-        <v>0.87064676616915337</v>
+        <v>0.87064676616915338</v>
       </c>
       <c r="CW43" s="0">
         <v>0.060672248513529856</v>
@@ -15749,10 +15750,10 @@
         <v>0.21736505252988753</v>
       </c>
       <c r="B44" s="0">
-        <v>0.20906506104699762</v>
+        <v>0.20906506104699763</v>
       </c>
       <c r="C44" s="0">
-        <v>0.31816173221387511</v>
+        <v>0.31816173221387512</v>
       </c>
       <c r="D44" s="0">
         <v>0.15026090757588162</v>
@@ -15791,7 +15792,7 @@
         <v>0.2175202689341505</v>
       </c>
       <c r="P44" s="0">
-        <v>0.30711482682136126</v>
+        <v>0.30711482682136127</v>
       </c>
       <c r="Q44" s="0">
         <v>0.30864197530864168</v>
@@ -15896,7 +15897,7 @@
         <v>1.0128633647320968</v>
       </c>
       <c r="AY44" s="0">
-        <v>1.0178631614425337</v>
+        <v>1.0178631614425338</v>
       </c>
       <c r="AZ44" s="0">
         <v>0.93244411510435876</v>
@@ -16022,7 +16023,7 @@
         <v>0.69394592007657274</v>
       </c>
       <c r="CO44" s="0">
-        <v>0.40553645420082834</v>
+        <v>0.40553645420082835</v>
       </c>
       <c r="CP44" s="0">
         <v>1.135228044929447</v>
@@ -16165,7 +16166,7 @@
         <v>0.23683477291724692</v>
       </c>
       <c r="T45" s="0">
-        <v>0.21853445332240642</v>
+        <v>0.21853445332240643</v>
       </c>
       <c r="U45" s="0">
         <v>0.52054285183119497</v>
@@ -16270,7 +16271,7 @@
         <v>1.094027202838556</v>
       </c>
       <c r="BC45" s="0">
-        <v>0.87184696123243532</v>
+        <v>0.87184696123243533</v>
       </c>
       <c r="BD45" s="0">
         <v>0.63720452209660783</v>
@@ -16351,7 +16352,7 @@
         <v>0.74990626171728458</v>
       </c>
       <c r="CD45" s="0">
-        <v>0.8846153846153838</v>
+        <v>0.88461538461538381</v>
       </c>
       <c r="CE45" s="0">
         <v>1.4603174603174591</v>
@@ -16488,7 +16489,7 @@
         <v>0.14346790622937741</v>
       </c>
       <c r="G46" s="0">
-        <v>0.1335470085470094</v>
+        <v>0.13354700854700941</v>
       </c>
       <c r="H46" s="0">
         <v>0.13119386416389228</v>
@@ -16527,7 +16528,7 @@
         <v>0.19039658214916069</v>
       </c>
       <c r="T46" s="0">
-        <v>0.15024243665915551</v>
+        <v>0.15024243665915552</v>
       </c>
       <c r="U46" s="0">
         <v>0.52054285183119875</v>
@@ -16560,7 +16561,7 @@
         <v>0.54722817035451221</v>
       </c>
       <c r="AE46" s="0">
-        <v>0.81967213114754633</v>
+        <v>0.81967213114754634</v>
       </c>
       <c r="AF46" s="0">
         <v>0.91228070175439191</v>
@@ -16569,7 +16570,7 @@
         <v>0.59604647653538945</v>
       </c>
       <c r="AH46" s="0">
-        <v>1.2765620044402239</v>
+        <v>1.276562004440224</v>
       </c>
       <c r="AI46" s="0">
         <v>0.2939089895611654</v>
@@ -16614,7 +16615,7 @@
         <v>0.81228109397124015</v>
       </c>
       <c r="AW46" s="0">
-        <v>0.55615357014711519</v>
+        <v>0.5561535701471152</v>
       </c>
       <c r="AX46" s="0">
         <v>0.67861845437050983</v>
@@ -16647,7 +16648,7 @@
         <v>0.91189155884165718</v>
       </c>
       <c r="BH46" s="0">
-        <v>0.51316376617581771</v>
+        <v>0.51316376617581772</v>
       </c>
       <c r="BI46" s="0">
         <v>0.86426394118702377</v>
@@ -16680,7 +16681,7 @@
         <v>1.0010494873657934</v>
       </c>
       <c r="BS46" s="0">
-        <v>0.36754311563472108</v>
+        <v>0.36754311563472109</v>
       </c>
       <c r="BT46" s="0">
         <v>0.46213855677096882</v>
@@ -16707,7 +16708,7 @@
         <v>0.2005012531328334</v>
       </c>
       <c r="CB46" s="0">
-        <v>1.4173228346456785</v>
+        <v>1.4173228346456786</v>
       </c>
       <c r="CC46" s="0">
         <v>0.48743907011623866</v>
@@ -16731,7 +16732,7 @@
         <v>0.58790904048807924</v>
       </c>
       <c r="CJ46" s="0">
-        <v>1.1068943706514935</v>
+        <v>1.1068943706514936</v>
       </c>
       <c r="CK46" s="0">
         <v>1.2601106853980499</v>
@@ -16958,7 +16959,7 @@
         <v>1.1479028697571734</v>
       </c>
       <c r="AQ47" s="0">
-        <v>0.55793991416308963</v>
+        <v>0.55793991416308964</v>
       </c>
       <c r="AR47" s="0">
         <v>1.1090342679127718</v>
@@ -17015,7 +17016,7 @@
         <v>0.78536847767616924</v>
       </c>
       <c r="BJ47" s="0">
-        <v>0.64492353049566919</v>
+        <v>0.6449235304956692</v>
       </c>
       <c r="BK47" s="0">
         <v>1.1813998214163051</v>
@@ -17042,7 +17043,7 @@
         <v>1.0575603455235318</v>
       </c>
       <c r="BS47" s="0">
-        <v>0.29080334423845849</v>
+        <v>0.2908033442384585</v>
       </c>
       <c r="BT47" s="0">
         <v>0.41974052403968415</v>
@@ -17054,7 +17055,7 @@
         <v>0.22932022932022911</v>
       </c>
       <c r="BW47" s="0">
-        <v>0.04385964912280698</v>
+        <v>0.043859649122806981</v>
       </c>
       <c r="BX47" s="0">
         <v>0.72921048941242395</v>
@@ -17362,7 +17363,7 @@
         <v>0.47961630695443602</v>
       </c>
       <c r="BE48" s="0">
-        <v>0.031254883575558653</v>
+        <v>0.031254883575558654</v>
       </c>
       <c r="BF48" s="0">
         <v>0.22212966819380794</v>
@@ -17374,7 +17375,7 @@
         <v>0.35698348951360964</v>
       </c>
       <c r="BI48" s="0">
-        <v>0.64550833781602956</v>
+        <v>0.64550833781602957</v>
       </c>
       <c r="BJ48" s="0">
         <v>0.58964437073889753</v>
@@ -17404,7 +17405,7 @@
         <v>1.1302171631549194</v>
       </c>
       <c r="BS48" s="0">
-        <v>0.27868653822852268</v>
+        <v>0.27868653822852269</v>
       </c>
       <c r="BT48" s="0">
         <v>0.29254642584584051</v>
@@ -17416,7 +17417,7 @@
         <v>0.26208026208026186</v>
       </c>
       <c r="BW48" s="0">
-        <v>0.04385964912280698</v>
+        <v>0.043859649122806981</v>
       </c>
       <c r="BX48" s="0">
         <v>0.63104753891459764</v>
@@ -17467,7 +17468,7 @@
         <v>0.8198248555990304</v>
       </c>
       <c r="CN48" s="0">
-        <v>0.40679588418281853</v>
+        <v>0.40679588418281854</v>
       </c>
       <c r="CO48" s="0">
         <v>0.18513620735255207</v>
@@ -17577,13 +17578,13 @@
         <v>0.053418803418803368</v>
       </c>
       <c r="H49" s="0">
-        <v>0.050459178524573572</v>
+        <v>0.050459178524573573</v>
       </c>
       <c r="I49" s="0">
         <v>0.07751937984496117</v>
       </c>
       <c r="J49" s="0">
-        <v>0.044759895133959927</v>
+        <v>0.044759895133959928</v>
       </c>
       <c r="K49" s="0">
         <v>0.057012542759407023</v>
@@ -17640,7 +17641,7 @@
         <v>0.24524831391784158</v>
       </c>
       <c r="AC49" s="0">
-        <v>0.59101654846335649</v>
+        <v>0.5910165484633565</v>
       </c>
       <c r="AD49" s="0">
         <v>0.49964311206281187</v>
@@ -17799,7 +17800,7 @@
         <v>0.36245469316335427</v>
       </c>
       <c r="CD49" s="0">
-        <v>0.64102564102564052</v>
+        <v>0.64102564102564053</v>
       </c>
       <c r="CE49" s="0">
         <v>0.31746031746031722</v>
@@ -18080,7 +18081,7 @@
         <v>0.65050266114724964</v>
       </c>
       <c r="BC50" s="0">
-        <v>0.52480108346030085</v>
+        <v>0.52480108346030086</v>
       </c>
       <c r="BD50" s="0">
         <v>0.23980815347721801</v>
@@ -18110,7 +18111,7 @@
         <v>0.43943446694688537</v>
       </c>
       <c r="BM50" s="0">
-        <v>0.35343878556115615</v>
+        <v>0.35343878556115616</v>
       </c>
       <c r="BN50" s="0">
         <v>0.98313153265031483</v>
@@ -18176,7 +18177,7 @@
         <v>0.40634247603904389</v>
       </c>
       <c r="CI50" s="0">
-        <v>0.26622296173044901</v>
+        <v>0.26622296173044902</v>
       </c>
       <c r="CJ50" s="0">
         <v>0.62196921779464409</v>
@@ -18301,7 +18302,7 @@
         <v>0.066773504273504203</v>
       </c>
       <c r="H51" s="0">
-        <v>0.050459178524573572</v>
+        <v>0.050459178524573573</v>
       </c>
       <c r="I51" s="0">
         <v>0.044296788482834956</v>
@@ -18319,7 +18320,7 @@
         <v>0.097020097020096938</v>
       </c>
       <c r="N51" s="0">
-        <v>0.041536863966770476</v>
+        <v>0.041536863966770477</v>
       </c>
       <c r="O51" s="0">
         <v>0.01977456990310459</v>
@@ -18361,7 +18362,7 @@
         <v>1.0554089709762524</v>
       </c>
       <c r="AB51" s="0">
-        <v>0.20437359493153467</v>
+        <v>0.20437359493153468</v>
       </c>
       <c r="AC51" s="0">
         <v>0.42553191489361664</v>
@@ -18385,7 +18386,7 @@
         <v>0.18242626938279097</v>
       </c>
       <c r="AJ51" s="0">
-        <v>0.73271413828689302</v>
+        <v>0.73271413828689303</v>
       </c>
       <c r="AK51" s="0">
         <v>0.77260233266473444</v>
@@ -18403,7 +18404,7 @@
         <v>0.89887640449438122</v>
       </c>
       <c r="AP51" s="0">
-        <v>0.88300220750551794</v>
+        <v>0.88300220750551795</v>
       </c>
       <c r="AQ51" s="0">
         <v>0.28612303290414853</v>
@@ -18478,7 +18479,7 @@
         <v>0.85894649694711711</v>
       </c>
       <c r="BO51" s="0">
-        <v>0.66419002589215292</v>
+        <v>0.66419002589215293</v>
       </c>
       <c r="BP51" s="0">
         <v>0.19106407995296867</v>
@@ -18544,7 +18545,7 @@
         <v>0.96985030571368247</v>
       </c>
       <c r="CK51" s="0">
-        <v>0.83155952887753581</v>
+        <v>0.83155952887753582</v>
       </c>
       <c r="CL51" s="0">
         <v>0.43577112542629742</v>
@@ -18696,7 +18697,7 @@
         <v>0.13774104683195582</v>
       </c>
       <c r="S52" s="0">
-        <v>0.046438190768087632</v>
+        <v>0.046438190768087633</v>
       </c>
       <c r="T52" s="0">
         <v>0.040975209997951199</v>
@@ -18921,7 +18922,7 @@
         <v>0.11020012342413814</v>
       </c>
       <c r="CP52" s="0">
-        <v>0.38373905744093983</v>
+        <v>0.38373905744093984</v>
       </c>
       <c r="CQ52" s="0">
         <v>0</v>
@@ -19130,7 +19131,7 @@
         <v>0.69168506254598905</v>
       </c>
       <c r="AQ53" s="0">
-        <v>0.2288984263233188</v>
+        <v>0.22889842632331881</v>
       </c>
       <c r="AR53" s="0">
         <v>0.48598130841121451</v>
@@ -19166,7 +19167,7 @@
         <v>0.39424403705893912</v>
       </c>
       <c r="BC53" s="0">
-        <v>0.36397494498053123</v>
+        <v>0.36397494498053124</v>
       </c>
       <c r="BD53" s="0">
         <v>0.19184652278177441</v>
@@ -19196,13 +19197,13 @@
         <v>0.34390523500191028</v>
       </c>
       <c r="BM53" s="0">
-        <v>0.18541051045831144</v>
+        <v>0.18541051045831145</v>
       </c>
       <c r="BN53" s="0">
         <v>0.64162268446652126</v>
       </c>
       <c r="BO53" s="0">
-        <v>0.30395136778115472</v>
+        <v>0.30395136778115473</v>
       </c>
       <c r="BP53" s="0">
         <v>0.11022927689594346</v>
@@ -19280,7 +19281,7 @@
         <v>0.10768126346015784</v>
       </c>
       <c r="CO53" s="0">
-        <v>0.070528078991448417</v>
+        <v>0.070528078991448418</v>
       </c>
       <c r="CP53" s="0">
         <v>0.33177439341247922</v>
@@ -19441,7 +19442,7 @@
         <v>0.078616352201257789</v>
       </c>
       <c r="Z54" s="0">
-        <v>0.75497597803706173</v>
+        <v>0.75497597803706174</v>
       </c>
       <c r="AA54" s="0">
         <v>0.85019055995309212</v>
@@ -19851,7 +19852,7 @@
         <v>0.35955056179775513</v>
       </c>
       <c r="AP55" s="0">
-        <v>0.5739514348785909</v>
+        <v>0.57395143487859091</v>
       </c>
       <c r="AQ55" s="0">
         <v>0.17167381974249038</v>
@@ -19869,10 +19870,10 @@
         <v>0.037091988130564038</v>
       </c>
       <c r="AV55" s="0">
-        <v>0.19375512333258937</v>
+        <v>0.19375512333258938</v>
       </c>
       <c r="AW55" s="0">
-        <v>0.17043415859347077</v>
+        <v>0.17043415859347078</v>
       </c>
       <c r="AX55" s="0">
         <v>0.18231540565177878</v>
@@ -19992,7 +19993,7 @@
         <v>0.33733923676997901</v>
       </c>
       <c r="CK55" s="0">
-        <v>0.50517950901092989</v>
+        <v>0.5051795090109299</v>
       </c>
       <c r="CL55" s="0">
         <v>0.20525451559934454</v>
@@ -20264,7 +20265,7 @@
         <v>0.027766208524225993</v>
       </c>
       <c r="BG56" s="0">
-        <v>0.30807147258163869</v>
+        <v>0.3080714725816387</v>
       </c>
       <c r="BH56" s="0">
         <v>0.044622936189201205</v>
@@ -20488,7 +20489,7 @@
         <v>0</v>
       </c>
       <c r="M57" s="0">
-        <v>0.027720027720027698</v>
+        <v>0.027720027720027699</v>
       </c>
       <c r="N57" s="0">
         <v>0</v>
@@ -20611,7 +20612,7 @@
         <v>0.062912865681031716</v>
       </c>
       <c r="BB57" s="0">
-        <v>0.24640252316183694</v>
+        <v>0.24640252316183695</v>
       </c>
       <c r="BC57" s="0">
         <v>0.076180802437785605</v>
@@ -21263,7 +21264,7 @@
         <v>0.047281323877068522</v>
       </c>
       <c r="AD59" s="0">
-        <v>0.071377587437544548</v>
+        <v>0.071377587437544549</v>
       </c>
       <c r="AE59" s="0">
         <v>0.068306010928961686</v>
@@ -21377,7 +21378,7 @@
         <v>0.10131712259371825</v>
       </c>
       <c r="BP59" s="0">
-        <v>0.02204585537918869</v>
+        <v>0.022045855379188691</v>
       </c>
       <c r="BQ59" s="0">
         <v>0.035893754486719276</v>
@@ -21574,7 +21575,7 @@
         <v>0</v>
       </c>
       <c r="M60" s="0">
-        <v>0.027720027720027698</v>
+        <v>0.027720027720027699</v>
       </c>
       <c r="N60" s="0">
         <v>0</v>
@@ -21655,7 +21656,7 @@
         <v>0</v>
       </c>
       <c r="AN60" s="0">
-        <v>0.17383746197305502</v>
+        <v>0.17383746197305503</v>
       </c>
       <c r="AO60" s="0">
         <v>0.2546816479400747</v>
@@ -21751,7 +21752,7 @@
         <v>0.0040389353366452564</v>
       </c>
       <c r="BT60" s="0">
-        <v>0.0084796065462562457</v>
+        <v>0.0084796065462562458</v>
       </c>
       <c r="BU60" s="0">
         <v>0.051808102787275885</v>
@@ -21769,13 +21770,13 @@
         <v>0.013935340022296532</v>
       </c>
       <c r="BZ60" s="0">
-        <v>0.026329647182727726</v>
+        <v>0.026329647182727727</v>
       </c>
       <c r="CA60" s="0">
         <v>0</v>
       </c>
       <c r="CB60" s="0">
-        <v>0.052493438320209924</v>
+        <v>0.052493438320209925</v>
       </c>
       <c r="CC60" s="0">
         <v>0.012498437695288078</v>
@@ -22020,7 +22021,7 @@
         <v>0.043459365493263756</v>
       </c>
       <c r="AO61" s="0">
-        <v>0.089887640449438116</v>
+        <v>0.089887640449438117</v>
       </c>
       <c r="AP61" s="0">
         <v>0.26490066225165537</v>
@@ -22062,7 +22063,7 @@
         <v>0.10841711019120827</v>
       </c>
       <c r="BC61" s="0">
-        <v>0.05078720162519041</v>
+        <v>0.050787201625190411</v>
       </c>
       <c r="BD61" s="0">
         <v>0.027406646111682059</v>
@@ -22164,7 +22165,7 @@
         <v>0.13704406493780297</v>
       </c>
       <c r="CK61" s="0">
-        <v>0.22420888321271445</v>
+        <v>0.22420888321271446</v>
       </c>
       <c r="CL61" s="0">
         <v>0.066312997347480043</v>
@@ -22328,7 +22329,7 @@
         <v>0</v>
       </c>
       <c r="W62" s="0">
-        <v>0.085470085470085388</v>
+        <v>0.085470085470085389</v>
       </c>
       <c r="X62" s="0">
         <v>0</v>
@@ -22403,7 +22404,7 @@
         <v>0</v>
       </c>
       <c r="AV62" s="0">
-        <v>0.0074521201281764603</v>
+        <v>0.0074521201281764604</v>
       </c>
       <c r="AW62" s="0">
         <v>0</v>
@@ -22499,7 +22500,7 @@
         <v>0</v>
       </c>
       <c r="CB62" s="0">
-        <v>0.052493438320209924</v>
+        <v>0.052493438320209925</v>
       </c>
       <c r="CC62" s="0">
         <v>0.012498437695288078</v>
@@ -22523,7 +22524,7 @@
         <v>0</v>
       </c>
       <c r="CJ62" s="0">
-        <v>0.084334809192494128</v>
+        <v>0.084334809192494129</v>
       </c>
       <c r="CK62" s="0">
         <v>0.14758053072229305</v>
@@ -22834,7 +22835,7 @@
         <v>0.056510858157746389</v>
       </c>
       <c r="BS63" s="0">
-        <v>0.0040389353366452867</v>
+        <v>0.0040389353366452868</v>
       </c>
       <c r="BT63" s="0">
         <v>0</v>
@@ -22885,7 +22886,7 @@
         <v>0.022185246810870914</v>
       </c>
       <c r="CJ63" s="0">
-        <v>0.042167404596247376</v>
+        <v>0.042167404596247377</v>
       </c>
       <c r="CK63" s="0">
         <v>0.14758053072229416</v>
@@ -23414,7 +23415,7 @@
         <v>0</v>
       </c>
       <c r="W65" s="0">
-        <v>0.085470085470085388</v>
+        <v>0.085470085470085389</v>
       </c>
       <c r="X65" s="0">
         <v>0</v>
@@ -23489,7 +23490,7 @@
         <v>0</v>
       </c>
       <c r="AV65" s="0">
-        <v>0.0074521201281764603</v>
+        <v>0.0074521201281764604</v>
       </c>
       <c r="AW65" s="0">
         <v>0.0089702188733405009</v>
@@ -23561,7 +23562,7 @@
         <v>0</v>
       </c>
       <c r="BT65" s="0">
-        <v>0.0084796065462562457</v>
+        <v>0.0084796065462562458</v>
       </c>
       <c r="BU65" s="0">
         <v>0</v>
@@ -24150,7 +24151,7 @@
         <v>0.022878059940517191</v>
       </c>
       <c r="AA67" s="0">
-        <v>0.087950747581355015</v>
+        <v>0.087950747581355016</v>
       </c>
       <c r="AB67" s="0">
         <v>0</v>
@@ -24159,7 +24160,7 @@
         <v>0.023640661938534435</v>
       </c>
       <c r="AD67" s="0">
-        <v>0.023792529145848357</v>
+        <v>0.023792529145848358</v>
       </c>
       <c r="AE67" s="0">
         <v>0</v>
@@ -24282,7 +24283,7 @@
         <v>0.024218939210462739</v>
       </c>
       <c r="BS67" s="0">
-        <v>0.0040389353366452867</v>
+        <v>0.0040389353366452868</v>
       </c>
       <c r="BT67" s="0">
         <v>0.0042398032731281541</v>
@@ -24695,7 +24696,7 @@
         <v>0.022185246810870588</v>
       </c>
       <c r="CJ68" s="0">
-        <v>0.031625553447185067</v>
+        <v>0.031625553447185068</v>
       </c>
       <c r="CK68" s="0">
         <v>0.034057045551298147</v>
@@ -24901,7 +24902,7 @@
         <v>0</v>
       </c>
       <c r="AJ69" s="0">
-        <v>0.030959752321981625</v>
+        <v>0.030959752321981626</v>
       </c>
       <c r="AK69" s="0">
         <v>0.029715474333259238</v>
@@ -25257,7 +25258,7 @@
         <v>0</v>
       </c>
       <c r="AH70" s="0">
-        <v>0.023786869647954133</v>
+        <v>0.023786869647954134</v>
       </c>
       <c r="AI70" s="0">
         <v>0</v>
@@ -25419,7 +25420,7 @@
         <v>0</v>
       </c>
       <c r="CJ70" s="0">
-        <v>0.031625553447185067</v>
+        <v>0.031625553447185068</v>
       </c>
       <c r="CK70" s="0">
         <v>0.022704697034198761</v>
